--- a/MinMax/scripts/comparison/accuracy_comparison_table_118_5_True.xlsx
+++ b/MinMax/scripts/comparison/accuracy_comparison_table_118_5_True.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="35">
   <si>
     <t>Pg Vm Projection True</t>
   </si>
@@ -31,85 +31,94 @@
     <t>Metric [MSE]</t>
   </si>
   <si>
+    <t>sample_num</t>
+  </si>
+  <si>
+    <t>qd_tot</t>
+  </si>
+  <si>
     <t>pinj_tot</t>
   </si>
   <si>
+    <t>Ibr_from_i_tot</t>
+  </si>
+  <si>
+    <t>Iinj_r_tot</t>
+  </si>
+  <si>
+    <t>vr_tot</t>
+  </si>
+  <si>
+    <t>Iinj_i_tot</t>
+  </si>
+  <si>
+    <t>pg_tot</t>
+  </si>
+  <si>
     <t>pd_tot</t>
   </si>
   <si>
+    <t>Ibr_to_r_tot</t>
+  </si>
+  <si>
+    <t>Ibr_to_i_tot</t>
+  </si>
+  <si>
+    <t>solve_time</t>
+  </si>
+  <si>
+    <t>vi_tot</t>
+  </si>
+  <si>
+    <t>cost_tot</t>
+  </si>
+  <si>
+    <t>qinj_tot</t>
+  </si>
+  <si>
     <t>slack_tot</t>
   </si>
   <si>
-    <t>solve_time</t>
+    <t>qg_tot</t>
   </si>
   <si>
     <t>vm_tot</t>
   </si>
   <si>
-    <t>pg_tot</t>
-  </si>
-  <si>
-    <t>vi_tot</t>
-  </si>
-  <si>
-    <t>cost_tot</t>
-  </si>
-  <si>
-    <t>qd_tot</t>
-  </si>
-  <si>
-    <t>qg_tot</t>
-  </si>
-  <si>
-    <t>vr_tot</t>
-  </si>
-  <si>
     <t>Ibr_from_r_tot</t>
   </si>
   <si>
-    <t>Ibr_from_i_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_r_tot</t>
-  </si>
-  <si>
-    <t>Iinj_i_tot</t>
-  </si>
-  <si>
-    <t>Ibr_to_i_tot</t>
-  </si>
-  <si>
-    <t>qinj_tot</t>
-  </si>
-  <si>
-    <t>Iinj_r_tot</t>
-  </si>
-  <si>
-    <t>2.33 (1.34)</t>
-  </si>
-  <si>
-    <t>1.15s (5.96 s)</t>
-  </si>
-  <si>
-    <t>87327.70 (67523.48 &gt; 29.50%)</t>
-  </si>
-  <si>
-    <t>1.35 (1.34)</t>
-  </si>
-  <si>
-    <t>71103.30 (67523.48 &gt; 5.14%)</t>
-  </si>
-  <si>
-    <t>1.33 (1.34)</t>
-  </si>
-  <si>
-    <t>5.00s (5.96 s)</t>
-  </si>
-  <si>
-    <t>67519.80 (67523.48 &gt; 0.01%)</t>
-  </si>
-  <si>
-    <t>3.07s (5.96 s)</t>
+    <t>0.14s (0.18 s)</t>
+  </si>
+  <si>
+    <t>87338.42 (67523.48 &gt; 29.35%)</t>
+  </si>
+  <si>
+    <t>233.05 (133.88)</t>
+  </si>
+  <si>
+    <t>0.19s (0.18 s)</t>
+  </si>
+  <si>
+    <t>71046.55 (67523.48 &gt; 5.22%)</t>
+  </si>
+  <si>
+    <t>134.72 (133.88)</t>
+  </si>
+  <si>
+    <t>0.16s (0.18 s)</t>
+  </si>
+  <si>
+    <t>67523.33 (67523.48 &gt; 0.00%)</t>
+  </si>
+  <si>
+    <t>133.89 (133.88)</t>
+  </si>
+  <si>
+    <t>0.17s (0.18 s)</t>
+  </si>
+  <si>
+    <t>67523.34 (67523.48 &gt; 0.00%)</t>
   </si>
 </sst>
 </file>
@@ -467,7 +476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -491,68 +500,56 @@
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2">
-        <v>0.4252068400382996</v>
-      </c>
-      <c r="C2">
-        <v>0.01443591341376305</v>
-      </c>
-      <c r="D2">
-        <v>3.551632289600093E-06</v>
-      </c>
-      <c r="E2">
-        <v>3.551632289600093E-06</v>
-      </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B3">
-        <v>1.914293666701331E-16</v>
+        <v>0.0003574936708901078</v>
       </c>
       <c r="C3">
-        <v>1.914293666701331E-16</v>
+        <v>2.491211909892073E-17</v>
       </c>
       <c r="D3">
-        <v>1.914293666701331E-16</v>
+        <v>0.0003195077588316053</v>
       </c>
       <c r="E3">
-        <v>1.914293666701331E-16</v>
+        <v>0.0002004880807362497</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>28</v>
+      <c r="B4">
+        <v>0.4348416030406952</v>
+      </c>
+      <c r="C4">
+        <v>0.01427220646291971</v>
+      </c>
+      <c r="D4">
+        <v>0.02864724583923817</v>
+      </c>
+      <c r="E4">
+        <v>0.004571301862597466</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" t="s">
-        <v>31</v>
+      <c r="B5">
+        <v>0.08662581443786621</v>
+      </c>
+      <c r="C5">
+        <v>0.08646795153617859</v>
+      </c>
+      <c r="D5">
+        <v>0.08615988492965698</v>
+      </c>
+      <c r="E5">
+        <v>0.08614911884069443</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -560,16 +557,16 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>8.32808218547143E-05</v>
+        <v>0.3561009466648102</v>
       </c>
       <c r="C6">
-        <v>0.0003032834210898727</v>
+        <v>0.01099952962249517</v>
       </c>
       <c r="D6">
-        <v>1.105430055758916E-05</v>
+        <v>0.025923702865839</v>
       </c>
       <c r="E6">
-        <v>1.105430055758916E-05</v>
+        <v>0.004099946934729815</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -577,16 +574,16 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>0.9259239435195923</v>
+        <v>0.0005065568257123232</v>
       </c>
       <c r="C7">
-        <v>0.03077800013124943</v>
+        <v>0.0002912851632572711</v>
       </c>
       <c r="D7">
-        <v>6.847178156021982E-06</v>
+        <v>4.469668419915251E-05</v>
       </c>
       <c r="E7">
-        <v>6.847178156021982E-06</v>
+        <v>5.03870705870213E-06</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -594,33 +591,33 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>0.02039679698646069</v>
+        <v>0.06914884597063065</v>
       </c>
       <c r="C8">
-        <v>0.0002060235856333748</v>
+        <v>0.02456555142998695</v>
       </c>
       <c r="D8">
-        <v>1.450050262974401E-06</v>
+        <v>0.003605447476729751</v>
       </c>
       <c r="E8">
-        <v>1.450050262974401E-06</v>
+        <v>0.0005601905868388712</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E9" t="s">
-        <v>30</v>
+      <c r="B9">
+        <v>0.9380835890769958</v>
+      </c>
+      <c r="C9">
+        <v>0.03043651580810547</v>
+      </c>
+      <c r="D9">
+        <v>0.03836539760231972</v>
+      </c>
+      <c r="E9">
+        <v>0.00560062425211072</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -628,16 +625,16 @@
         <v>13</v>
       </c>
       <c r="B10">
-        <v>2.491211909892073E-17</v>
+        <v>0.003070825943723321</v>
       </c>
       <c r="C10">
-        <v>2.491211909892073E-17</v>
+        <v>1.914293666701331E-16</v>
       </c>
       <c r="D10">
-        <v>2.491211909892073E-17</v>
+        <v>0.003399760462343693</v>
       </c>
       <c r="E10">
-        <v>2.491211909892073E-17</v>
+        <v>0.001183772808872163</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -645,16 +642,16 @@
         <v>14</v>
       </c>
       <c r="B11">
-        <v>0.0418773777782917</v>
+        <v>0.5232213139533997</v>
       </c>
       <c r="C11">
-        <v>0.05940727517008781</v>
+        <v>0.5181781649589539</v>
       </c>
       <c r="D11">
-        <v>0.007935475558042526</v>
+        <v>0.5179413557052612</v>
       </c>
       <c r="E11">
-        <v>0.007935475558042526</v>
+        <v>0.517759382724762</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -662,33 +659,33 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>0.0001285248581552878</v>
+        <v>0.1010571047663689</v>
       </c>
       <c r="C12">
-        <v>0.0002965929161291569</v>
+        <v>0.100731797516346</v>
       </c>
       <c r="D12">
-        <v>1.049709590006387E-05</v>
+        <v>0.1004850044846535</v>
       </c>
       <c r="E12">
-        <v>1.049709590006387E-05</v>
+        <v>0.1004744693636894</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B13">
-        <v>0.2905104160308838</v>
-      </c>
-      <c r="C13">
-        <v>0.005250283516943455</v>
-      </c>
-      <c r="D13">
-        <v>1.754735058057122E-05</v>
-      </c>
-      <c r="E13">
-        <v>1.754735058057122E-05</v>
+      <c r="B13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" t="s">
+        <v>30</v>
+      </c>
+      <c r="E13" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -696,33 +693,33 @@
         <v>17</v>
       </c>
       <c r="B14">
-        <v>0.01940520107746124</v>
+        <v>0.02035165578126907</v>
       </c>
       <c r="C14">
-        <v>0.01349137257784605</v>
+        <v>0.0002060080441879109</v>
       </c>
       <c r="D14">
-        <v>0.001348192454315722</v>
+        <v>0.001805452979169786</v>
       </c>
       <c r="E14">
-        <v>0.001348192454315722</v>
+        <v>0.0002835611230693758</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B15">
-        <v>0.2760867178440094</v>
-      </c>
-      <c r="C15">
-        <v>0.004902237560600042</v>
-      </c>
-      <c r="D15">
-        <v>1.745270128594711E-05</v>
-      </c>
-      <c r="E15">
-        <v>1.745270128594711E-05</v>
+      <c r="B15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -730,33 +727,33 @@
         <v>19</v>
       </c>
       <c r="B16">
-        <v>0.06968007236719131</v>
+        <v>0.01983176730573177</v>
       </c>
       <c r="C16">
-        <v>0.03122517839074135</v>
+        <v>0.02477617003023624</v>
       </c>
       <c r="D16">
-        <v>0.006221320480108261</v>
+        <v>0.002893625060096383</v>
       </c>
       <c r="E16">
-        <v>0.006221320480108261</v>
+        <v>0.0004608292656484991</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B17">
-        <v>0.01920066773891449</v>
-      </c>
-      <c r="C17">
-        <v>0.01317153032869101</v>
-      </c>
-      <c r="D17">
-        <v>0.001343585783615708</v>
-      </c>
-      <c r="E17">
-        <v>0.001343585783615708</v>
+      <c r="B17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -764,16 +761,16 @@
         <v>21</v>
       </c>
       <c r="B18">
-        <v>0.02211036719381809</v>
+        <v>0.03670937940478325</v>
       </c>
       <c r="C18">
-        <v>0.03173233941197395</v>
+        <v>0.04960450902581215</v>
       </c>
       <c r="D18">
-        <v>0.006805455312132835</v>
+        <v>0.007505482528358698</v>
       </c>
       <c r="E18">
-        <v>0.006805455312132835</v>
+        <v>0.001245133811607957</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -781,16 +778,33 @@
         <v>22</v>
       </c>
       <c r="B19">
-        <v>0.3498136103153229</v>
+        <v>0.0006676322082057595</v>
       </c>
       <c r="C19">
-        <v>0.01136681623756886</v>
+        <v>0.0002976350951939821</v>
       </c>
       <c r="D19">
-        <v>6.426431355066597E-05</v>
+        <v>7.3765932029346E-06</v>
       </c>
       <c r="E19">
-        <v>6.426431355066597E-05</v>
+        <v>8.888731031220232E-07</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20">
+        <v>0.5449073910713196</v>
+      </c>
+      <c r="C20">
+        <v>0.5395516157150269</v>
+      </c>
+      <c r="D20">
+        <v>0.5392939448356628</v>
+      </c>
+      <c r="E20">
+        <v>0.5391098856925964</v>
       </c>
     </row>
   </sheetData>
